--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-coquimbo.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3713-95-CM26</t>
+          <t>1305532-11-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>36317.99</v>
+        <v>24005.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3713-96-CM26</t>
+          <t>3707-90-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>762.03</v>
+        <v>70343.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3754-198-CM26</t>
+          <t>3512-2792-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,6 +691,1104 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
+        <v>32720.08</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3614-38-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>69.040.500-8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>17823.54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3512-2813-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>53204.41</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>646-33-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.816.000-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>24828.66</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3509-214-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>36525.12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>539119-3510-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.505.720-9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>31850.29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1094-3-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>26458.93</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4784-16-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Comercial Motores de los Andes SpA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>26312.26</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3842-19-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.040.900-3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>36157.82</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>624-204-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>24277.19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3712-769-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>POMPEYO CARRASCO SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>26904.32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3712-685-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>70601.14999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2448-745-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>42202.01</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3712-799-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>36460.55</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>624-318-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>72.225.700-6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>35782.52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>727202-3280-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.040.500-8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>35085.11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3713-96-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>762.03</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3713-95-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>36317.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3754-198-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>69.041.300-0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CANELA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>36103.2</v>
       </c>
     </row>
